--- a/backend/data/financials_by_company/1OP.F.xlsx
+++ b/backend/data/financials_by_company/1OP.F.xlsx
@@ -637,522 +637,522 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.342</v>
+        <v>0.28</v>
       </c>
       <c r="D2" t="n">
-        <v>23621000</v>
+        <v>16267000</v>
       </c>
       <c r="E2" t="n">
-        <v>11531000</v>
+        <v>11118000</v>
       </c>
       <c r="F2" t="n">
-        <v>1359000</v>
+        <v>1169000</v>
       </c>
       <c r="G2" t="n">
-        <v>23621000</v>
+        <v>16267000</v>
       </c>
       <c r="H2" t="n">
-        <v>22262000</v>
+        <v>15098000</v>
       </c>
       <c r="I2" t="n">
-        <v>1194000</v>
+        <v>-1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1367000</v>
+        <v>56000</v>
       </c>
       <c r="K2" t="n">
-        <v>11531000</v>
+        <v>11118000</v>
       </c>
       <c r="L2" t="n">
-        <v>11531000</v>
+        <v>11118000</v>
       </c>
       <c r="M2" t="n">
-        <v>111634688</v>
+        <v>112303030</v>
       </c>
       <c r="N2" t="n">
-        <v>111634688</v>
+        <v>110485465</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1051</v>
+        <v>0.099</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1061</v>
+        <v>0.1006</v>
       </c>
       <c r="Q2" t="n">
-        <v>11531000</v>
+        <v>11118000</v>
       </c>
       <c r="R2" t="n">
-        <v>11531000</v>
+        <v>11118000</v>
       </c>
       <c r="S2" t="n">
-        <v>11531000</v>
+        <v>11118000</v>
       </c>
       <c r="T2" t="n">
-        <v>11531000</v>
+        <v>11118000</v>
       </c>
       <c r="U2" t="n">
-        <v>6003000</v>
+        <v>4378000</v>
       </c>
       <c r="V2" t="n">
-        <v>17534000</v>
+        <v>15496000</v>
       </c>
       <c r="W2" t="n">
-        <v>-6161000</v>
+        <v>399000</v>
       </c>
       <c r="X2" t="n">
-        <v>-6161000</v>
+        <v>399000</v>
       </c>
       <c r="Y2" t="n">
-        <v>1194000</v>
+        <v>-1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>173000</v>
+        <v>57000</v>
       </c>
       <c r="AA2" t="n">
-        <v>1367000</v>
+        <v>56000</v>
       </c>
       <c r="AB2" t="n">
-        <v>22262000</v>
+        <v>15098000</v>
       </c>
       <c r="AC2" t="n">
-        <v>76862000</v>
+        <v>43557000</v>
       </c>
       <c r="AD2" t="n">
-        <v>31841000</v>
+        <v>18412000</v>
       </c>
       <c r="AE2" t="n">
-        <v>1359000</v>
+        <v>1169000</v>
       </c>
       <c r="AF2" t="n">
-        <v>1359000</v>
+        <v>1169000</v>
       </c>
       <c r="AG2" t="n">
-        <v>239000</v>
+        <v>95000</v>
       </c>
       <c r="AH2" t="n">
-        <v>239000</v>
+        <v>95000</v>
       </c>
       <c r="AI2" t="n">
-        <v>1120000</v>
+        <v>1074000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>43662000</v>
+        <v>23976000</v>
       </c>
       <c r="AK2" t="n">
-        <v>9121000</v>
+        <v>4951000</v>
       </c>
       <c r="AL2" t="n">
-        <v>34541000</v>
+        <v>19025000</v>
       </c>
       <c r="AM2" t="n">
-        <v>685000</v>
+        <v>258000</v>
       </c>
       <c r="AN2" t="n">
-        <v>33856000</v>
+        <v>18767000</v>
       </c>
       <c r="AO2" t="n">
-        <v>99124000</v>
+        <v>58655000</v>
       </c>
       <c r="AP2" t="n">
-        <v>99124000</v>
+        <v>58655000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>99124000</v>
+        <v>58655000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.379</v>
+        <v>0.308</v>
       </c>
       <c r="D3" t="n">
-        <v>14522000</v>
+        <v>15219000</v>
       </c>
       <c r="E3" t="n">
-        <v>6576000</v>
+        <v>9511000</v>
       </c>
       <c r="F3" t="n">
-        <v>1265000</v>
+        <v>1205000</v>
       </c>
       <c r="G3" t="n">
-        <v>14522000</v>
+        <v>15219000</v>
       </c>
       <c r="H3" t="n">
-        <v>13257000</v>
+        <v>14014000</v>
       </c>
       <c r="I3" t="n">
-        <v>692000</v>
+        <v>26000</v>
       </c>
       <c r="J3" t="n">
-        <v>780000</v>
+        <v>67000</v>
       </c>
       <c r="K3" t="n">
-        <v>6576000</v>
+        <v>9511000</v>
       </c>
       <c r="L3" t="n">
-        <v>6576000</v>
+        <v>9511000</v>
       </c>
       <c r="M3" t="n">
-        <v>112602740</v>
+        <v>112290437</v>
       </c>
       <c r="N3" t="n">
-        <v>111552062</v>
+        <v>111013492</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0584</v>
+        <v>0.0847</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0589</v>
+        <v>0.0857</v>
       </c>
       <c r="Q3" t="n">
-        <v>6576000</v>
+        <v>9511000</v>
       </c>
       <c r="R3" t="n">
-        <v>6576000</v>
+        <v>9511000</v>
       </c>
       <c r="S3" t="n">
-        <v>6576000</v>
+        <v>9511000</v>
       </c>
       <c r="T3" t="n">
-        <v>6576000</v>
+        <v>9511000</v>
       </c>
       <c r="U3" t="n">
-        <v>4006000</v>
+        <v>4263000</v>
       </c>
       <c r="V3" t="n">
-        <v>10582000</v>
-      </c>
-      <c r="W3" t="n">
-        <v>-2600000</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-2600000</v>
-      </c>
+        <v>13774000</v>
+      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
-        <v>692000</v>
+        <v>26000</v>
       </c>
       <c r="Z3" t="n">
-        <v>88000</v>
+        <v>41000</v>
       </c>
       <c r="AA3" t="n">
-        <v>780000</v>
+        <v>67000</v>
       </c>
       <c r="AB3" t="n">
-        <v>13257000</v>
+        <v>14014000</v>
       </c>
       <c r="AC3" t="n">
-        <v>67059000</v>
+        <v>56703000</v>
       </c>
       <c r="AD3" t="n">
-        <v>24614000</v>
+        <v>20862000</v>
       </c>
       <c r="AE3" t="n">
-        <v>1265000</v>
+        <v>1205000</v>
       </c>
       <c r="AF3" t="n">
-        <v>1265000</v>
+        <v>1205000</v>
       </c>
       <c r="AG3" t="n">
-        <v>231000</v>
+        <v>108000</v>
       </c>
       <c r="AH3" t="n">
-        <v>231000</v>
+        <v>108000</v>
       </c>
       <c r="AI3" t="n">
-        <v>1034000</v>
+        <v>1097000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>41180000</v>
+        <v>34636000</v>
       </c>
       <c r="AK3" t="n">
-        <v>11808000</v>
+        <v>9094000</v>
       </c>
       <c r="AL3" t="n">
-        <v>29372000</v>
+        <v>25542000</v>
       </c>
       <c r="AM3" t="n">
-        <v>446000</v>
+        <v>335000</v>
       </c>
       <c r="AN3" t="n">
-        <v>28926000</v>
+        <v>25207000</v>
       </c>
       <c r="AO3" t="n">
-        <v>80316000</v>
+        <v>70717000</v>
       </c>
       <c r="AP3" t="n">
-        <v>80316000</v>
+        <v>70717000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>80316000</v>
+        <v>70717000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0.308</v>
+        <v>0.379</v>
       </c>
       <c r="D4" t="n">
-        <v>15219000</v>
+        <v>14522000</v>
       </c>
       <c r="E4" t="n">
-        <v>9511000</v>
+        <v>6576000</v>
       </c>
       <c r="F4" t="n">
-        <v>1205000</v>
+        <v>1265000</v>
       </c>
       <c r="G4" t="n">
-        <v>15219000</v>
+        <v>14522000</v>
       </c>
       <c r="H4" t="n">
-        <v>14014000</v>
+        <v>13257000</v>
       </c>
       <c r="I4" t="n">
-        <v>26000</v>
+        <v>692000</v>
       </c>
       <c r="J4" t="n">
-        <v>67000</v>
+        <v>780000</v>
       </c>
       <c r="K4" t="n">
-        <v>9511000</v>
+        <v>6576000</v>
       </c>
       <c r="L4" t="n">
-        <v>9511000</v>
+        <v>6576000</v>
       </c>
       <c r="M4" t="n">
-        <v>112290437</v>
+        <v>112602740</v>
       </c>
       <c r="N4" t="n">
-        <v>111013492</v>
+        <v>111552062</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0847</v>
+        <v>0.0584</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0857</v>
+        <v>0.0589</v>
       </c>
       <c r="Q4" t="n">
-        <v>9511000</v>
+        <v>6576000</v>
       </c>
       <c r="R4" t="n">
-        <v>9511000</v>
+        <v>6576000</v>
       </c>
       <c r="S4" t="n">
-        <v>9511000</v>
+        <v>6576000</v>
       </c>
       <c r="T4" t="n">
-        <v>9511000</v>
+        <v>6576000</v>
       </c>
       <c r="U4" t="n">
-        <v>4263000</v>
+        <v>4006000</v>
       </c>
       <c r="V4" t="n">
-        <v>13774000</v>
-      </c>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
+        <v>10582000</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-2600000</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-2600000</v>
+      </c>
       <c r="Y4" t="n">
-        <v>26000</v>
+        <v>692000</v>
       </c>
       <c r="Z4" t="n">
-        <v>41000</v>
+        <v>88000</v>
       </c>
       <c r="AA4" t="n">
-        <v>67000</v>
+        <v>780000</v>
       </c>
       <c r="AB4" t="n">
-        <v>14014000</v>
+        <v>13257000</v>
       </c>
       <c r="AC4" t="n">
-        <v>56703000</v>
+        <v>67059000</v>
       </c>
       <c r="AD4" t="n">
-        <v>20862000</v>
+        <v>24614000</v>
       </c>
       <c r="AE4" t="n">
-        <v>1205000</v>
+        <v>1265000</v>
       </c>
       <c r="AF4" t="n">
-        <v>1205000</v>
+        <v>1265000</v>
       </c>
       <c r="AG4" t="n">
-        <v>108000</v>
+        <v>231000</v>
       </c>
       <c r="AH4" t="n">
-        <v>108000</v>
+        <v>231000</v>
       </c>
       <c r="AI4" t="n">
-        <v>1097000</v>
+        <v>1034000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>34636000</v>
+        <v>41180000</v>
       </c>
       <c r="AK4" t="n">
-        <v>9094000</v>
+        <v>11808000</v>
       </c>
       <c r="AL4" t="n">
-        <v>25542000</v>
+        <v>29372000</v>
       </c>
       <c r="AM4" t="n">
-        <v>335000</v>
+        <v>446000</v>
       </c>
       <c r="AN4" t="n">
-        <v>25207000</v>
+        <v>28926000</v>
       </c>
       <c r="AO4" t="n">
-        <v>70717000</v>
+        <v>80316000</v>
       </c>
       <c r="AP4" t="n">
-        <v>70717000</v>
+        <v>80316000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>70717000</v>
+        <v>80316000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0.28</v>
+        <v>0.342</v>
       </c>
       <c r="D5" t="n">
-        <v>16267000</v>
+        <v>23621000</v>
       </c>
       <c r="E5" t="n">
-        <v>11118000</v>
+        <v>11531000</v>
       </c>
       <c r="F5" t="n">
-        <v>1169000</v>
+        <v>1359000</v>
       </c>
       <c r="G5" t="n">
-        <v>16267000</v>
+        <v>23621000</v>
       </c>
       <c r="H5" t="n">
-        <v>15098000</v>
+        <v>22262000</v>
       </c>
       <c r="I5" t="n">
-        <v>-1000</v>
+        <v>1194000</v>
       </c>
       <c r="J5" t="n">
-        <v>56000</v>
+        <v>1367000</v>
       </c>
       <c r="K5" t="n">
-        <v>11118000</v>
+        <v>11531000</v>
       </c>
       <c r="L5" t="n">
-        <v>11118000</v>
+        <v>11531000</v>
       </c>
       <c r="M5" t="n">
-        <v>112303030</v>
+        <v>111634688</v>
       </c>
       <c r="N5" t="n">
-        <v>110485465</v>
+        <v>111634688</v>
       </c>
       <c r="O5" t="n">
-        <v>0.099</v>
+        <v>0.1051</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1006</v>
+        <v>0.1061</v>
       </c>
       <c r="Q5" t="n">
-        <v>11118000</v>
+        <v>11531000</v>
       </c>
       <c r="R5" t="n">
-        <v>11118000</v>
+        <v>11531000</v>
       </c>
       <c r="S5" t="n">
-        <v>11118000</v>
+        <v>11531000</v>
       </c>
       <c r="T5" t="n">
-        <v>11118000</v>
+        <v>11531000</v>
       </c>
       <c r="U5" t="n">
-        <v>4378000</v>
+        <v>6003000</v>
       </c>
       <c r="V5" t="n">
-        <v>15496000</v>
+        <v>17534000</v>
       </c>
       <c r="W5" t="n">
-        <v>399000</v>
+        <v>-6161000</v>
       </c>
       <c r="X5" t="n">
-        <v>399000</v>
+        <v>-6161000</v>
       </c>
       <c r="Y5" t="n">
-        <v>-1000</v>
+        <v>1194000</v>
       </c>
       <c r="Z5" t="n">
-        <v>57000</v>
+        <v>173000</v>
       </c>
       <c r="AA5" t="n">
-        <v>56000</v>
+        <v>1367000</v>
       </c>
       <c r="AB5" t="n">
-        <v>15098000</v>
+        <v>22262000</v>
       </c>
       <c r="AC5" t="n">
-        <v>43557000</v>
+        <v>76862000</v>
       </c>
       <c r="AD5" t="n">
-        <v>18412000</v>
+        <v>31841000</v>
       </c>
       <c r="AE5" t="n">
-        <v>1169000</v>
+        <v>1359000</v>
       </c>
       <c r="AF5" t="n">
-        <v>1169000</v>
+        <v>1359000</v>
       </c>
       <c r="AG5" t="n">
-        <v>95000</v>
+        <v>239000</v>
       </c>
       <c r="AH5" t="n">
-        <v>95000</v>
+        <v>239000</v>
       </c>
       <c r="AI5" t="n">
-        <v>1074000</v>
+        <v>1120000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>23976000</v>
+        <v>43662000</v>
       </c>
       <c r="AK5" t="n">
-        <v>4951000</v>
+        <v>9121000</v>
       </c>
       <c r="AL5" t="n">
-        <v>19025000</v>
+        <v>34541000</v>
       </c>
       <c r="AM5" t="n">
-        <v>258000</v>
+        <v>685000</v>
       </c>
       <c r="AN5" t="n">
-        <v>18767000</v>
+        <v>33856000</v>
       </c>
       <c r="AO5" t="n">
-        <v>58655000</v>
+        <v>99124000</v>
       </c>
       <c r="AP5" t="n">
-        <v>58655000</v>
+        <v>99124000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>58655000</v>
+        <v>99124000</v>
       </c>
     </row>
   </sheetData>
@@ -1493,375 +1493,383 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
-        <v>112782052</v>
+        <v>112387138</v>
       </c>
       <c r="C2" t="n">
-        <v>112782052</v>
+        <v>112387138</v>
       </c>
       <c r="D2" t="n">
-        <v>2770000</v>
+        <v>1574000</v>
       </c>
       <c r="E2" t="n">
-        <v>30144000</v>
+        <v>24180000</v>
       </c>
       <c r="F2" t="n">
-        <v>30144000</v>
+        <v>24180000</v>
       </c>
       <c r="G2" t="n">
-        <v>23654000</v>
+        <v>20083000</v>
       </c>
       <c r="H2" t="n">
-        <v>30144000</v>
+        <v>24180000</v>
       </c>
       <c r="I2" t="n">
-        <v>2770000</v>
+        <v>1574000</v>
       </c>
       <c r="J2" t="n">
-        <v>30144000</v>
+        <v>24180000</v>
       </c>
       <c r="K2" t="n">
-        <v>30144000</v>
+        <v>24180000</v>
       </c>
       <c r="L2" t="n">
-        <v>30144000</v>
+        <v>24180000</v>
       </c>
       <c r="M2" t="n">
-        <v>30144000</v>
+        <v>24180000</v>
       </c>
       <c r="N2" t="n">
-        <v>3459000</v>
+        <v>1034000</v>
       </c>
       <c r="O2" t="n">
-        <v>3459000</v>
-      </c>
-      <c r="P2" t="inlineStr"/>
+        <v>1033000</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1000</v>
+      </c>
       <c r="Q2" t="n">
-        <v>16449000</v>
+        <v>12470000</v>
       </c>
       <c r="R2" t="n">
-        <v>10236000</v>
+        <v>10676000</v>
       </c>
       <c r="S2" t="n">
-        <v>10236000</v>
+        <v>10676000</v>
       </c>
       <c r="T2" t="n">
-        <v>21090000</v>
+        <v>15286000</v>
       </c>
       <c r="U2" t="n">
-        <v>3069000</v>
+        <v>1339000</v>
       </c>
       <c r="V2" t="n">
-        <v>390000</v>
+        <v>218000</v>
       </c>
       <c r="W2" t="n">
-        <v>390000</v>
+        <v>218000</v>
       </c>
       <c r="X2" t="n">
-        <v>7000</v>
+        <v>35000</v>
       </c>
       <c r="Y2" t="n">
-        <v>7000</v>
+        <v>35000</v>
       </c>
       <c r="Z2" t="n">
-        <v>2180000</v>
+        <v>834000</v>
       </c>
       <c r="AA2" t="n">
-        <v>2180000</v>
+        <v>834000</v>
       </c>
       <c r="AB2" t="n">
-        <v>492000</v>
+        <v>252000</v>
       </c>
       <c r="AC2" t="n">
-        <v>18021000</v>
+        <v>13947000</v>
       </c>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="n">
-        <v>760000</v>
+        <v>1364000</v>
       </c>
       <c r="AF2" t="n">
-        <v>760000</v>
+        <v>1364000</v>
       </c>
       <c r="AG2" t="n">
-        <v>590000</v>
+        <v>740000</v>
       </c>
       <c r="AH2" t="n">
-        <v>590000</v>
+        <v>740000</v>
       </c>
       <c r="AI2" t="n">
-        <v>7429000</v>
+        <v>4593000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>9242000</v>
+        <v>7250000</v>
       </c>
       <c r="AK2" t="n">
-        <v>9242000</v>
+        <v>7250000</v>
       </c>
       <c r="AL2" t="n">
-        <v>1842000</v>
+        <v>1660000</v>
       </c>
       <c r="AM2" t="n">
-        <v>7400000</v>
+        <v>5590000</v>
       </c>
       <c r="AN2" t="n">
-        <v>50773000</v>
+        <v>39466000</v>
       </c>
       <c r="AO2" t="n">
-        <v>9098000</v>
+        <v>5436000</v>
       </c>
       <c r="AP2" t="n">
-        <v>4409000</v>
+        <v>2900000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4409000</v>
+        <v>2900000</v>
       </c>
       <c r="AR2" t="n">
-        <v>816000</v>
+        <v>645000</v>
       </c>
       <c r="AS2" t="n">
-        <v>816000</v>
-      </c>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
+        <v>643000</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>2000</v>
+      </c>
       <c r="AV2" t="n">
-        <v>3873000</v>
+        <v>1891000</v>
       </c>
       <c r="AW2" t="n">
-        <v>-461000</v>
+        <v>-1861000</v>
       </c>
       <c r="AX2" t="n">
-        <v>4334000</v>
+        <v>3752000</v>
       </c>
       <c r="AY2" t="n">
-        <v>662000</v>
+        <v>2294000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>3678000</v>
+        <v>1149000</v>
       </c>
       <c r="BA2" t="n">
-        <v>345000</v>
+        <v>309000</v>
       </c>
       <c r="BB2" t="n">
-        <v>41675000</v>
+        <v>34030000</v>
       </c>
       <c r="BC2" t="n">
-        <v>11000</v>
+        <v>626000</v>
       </c>
       <c r="BD2" t="inlineStr"/>
       <c r="BE2" t="inlineStr"/>
       <c r="BF2" t="n">
-        <v>1626000</v>
+        <v>909000</v>
       </c>
       <c r="BG2" t="n">
-        <v>3647000</v>
+        <v>4682000</v>
       </c>
       <c r="BH2" t="n">
-        <v>187000</v>
+        <v>3360000</v>
       </c>
       <c r="BI2" t="n">
-        <v>3460000</v>
+        <v>1322000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>36391000</v>
+        <v>27813000</v>
       </c>
       <c r="BK2" t="n">
-        <v>36391000</v>
+        <v>27813000</v>
       </c>
       <c r="BL2" t="n">
-        <v>36365000</v>
+        <v>27616000</v>
       </c>
       <c r="BM2" t="n">
-        <v>26000</v>
+        <v>197000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
-        <v>112782052</v>
+        <v>112387138</v>
       </c>
       <c r="C3" t="n">
-        <v>112782052</v>
+        <v>112387138</v>
       </c>
       <c r="D3" t="n">
-        <v>2202000</v>
+        <v>834000</v>
       </c>
       <c r="E3" t="n">
-        <v>26754000</v>
+        <v>24665000</v>
       </c>
       <c r="F3" t="n">
-        <v>26754000</v>
+        <v>24665000</v>
       </c>
       <c r="G3" t="n">
-        <v>18769000</v>
+        <v>14693000</v>
       </c>
       <c r="H3" t="n">
-        <v>26754000</v>
+        <v>24665000</v>
       </c>
       <c r="I3" t="n">
-        <v>2202000</v>
+        <v>834000</v>
       </c>
       <c r="J3" t="n">
-        <v>26754000</v>
+        <v>24665000</v>
       </c>
       <c r="K3" t="n">
-        <v>26754000</v>
+        <v>24665000</v>
       </c>
       <c r="L3" t="n">
-        <v>26754000</v>
+        <v>24665000</v>
       </c>
       <c r="M3" t="n">
-        <v>26754000</v>
+        <v>24665000</v>
       </c>
       <c r="N3" t="n">
-        <v>2301000</v>
+        <v>2706000</v>
       </c>
       <c r="O3" t="n">
-        <v>2293000</v>
+        <v>2702000</v>
       </c>
       <c r="P3" t="n">
-        <v>8000</v>
+        <v>4000</v>
       </c>
       <c r="Q3" t="n">
-        <v>13938000</v>
+        <v>12990000</v>
       </c>
       <c r="R3" t="n">
-        <v>10515000</v>
+        <v>8969000</v>
       </c>
       <c r="S3" t="n">
-        <v>10515000</v>
+        <v>8969000</v>
       </c>
       <c r="T3" t="n">
-        <v>20550000</v>
+        <v>17275000</v>
       </c>
       <c r="U3" t="n">
-        <v>2605000</v>
+        <v>623000</v>
       </c>
       <c r="V3" t="n">
-        <v>444000</v>
+        <v>284000</v>
       </c>
       <c r="W3" t="n">
-        <v>444000</v>
+        <v>284000</v>
       </c>
       <c r="X3" t="n">
-        <v>14000</v>
+        <v>34000</v>
       </c>
       <c r="Y3" t="n">
-        <v>14000</v>
+        <v>34000</v>
       </c>
       <c r="Z3" t="n">
-        <v>1823000</v>
+        <v>47000</v>
       </c>
       <c r="AA3" t="n">
-        <v>1823000</v>
+        <v>47000</v>
       </c>
       <c r="AB3" t="n">
-        <v>324000</v>
+        <v>258000</v>
       </c>
       <c r="AC3" t="n">
-        <v>17945000</v>
+        <v>16652000</v>
       </c>
       <c r="AD3" t="n">
-        <v>871000</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>605000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>605000</v>
-      </c>
+        <v>1300000</v>
+      </c>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="n">
-        <v>379000</v>
+        <v>787000</v>
       </c>
       <c r="AH3" t="n">
-        <v>379000</v>
+        <v>787000</v>
       </c>
       <c r="AI3" t="n">
-        <v>6258000</v>
+        <v>5997000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9832000</v>
+        <v>8568000</v>
       </c>
       <c r="AK3" t="n">
-        <v>9832000</v>
+        <v>8568000</v>
       </c>
       <c r="AL3" t="n">
-        <v>1323000</v>
+        <v>1815000</v>
       </c>
       <c r="AM3" t="n">
-        <v>8509000</v>
+        <v>6753000</v>
       </c>
       <c r="AN3" t="n">
-        <v>47304000</v>
+        <v>41940000</v>
       </c>
       <c r="AO3" t="n">
-        <v>10590000</v>
+        <v>10595000</v>
       </c>
       <c r="AP3" t="n">
-        <v>3974000</v>
+        <v>3338000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3974000</v>
+        <v>3338000</v>
       </c>
       <c r="AR3" t="n">
-        <v>3421000</v>
+        <v>5810000</v>
       </c>
       <c r="AS3" t="n">
-        <v>3419000</v>
+        <v>5809000</v>
       </c>
       <c r="AT3" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="AU3" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="AV3" t="n">
-        <v>3195000</v>
+        <v>1447000</v>
       </c>
       <c r="AW3" t="n">
-        <v>-2934000</v>
+        <v>-2435000</v>
       </c>
       <c r="AX3" t="n">
-        <v>6129000</v>
+        <v>3882000</v>
       </c>
       <c r="AY3" t="n">
         <v>2332000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>3488000</v>
+        <v>1186000</v>
       </c>
       <c r="BA3" t="n">
-        <v>309000</v>
+        <v>364000</v>
       </c>
       <c r="BB3" t="n">
-        <v>36714000</v>
+        <v>31345000</v>
       </c>
       <c r="BC3" t="n">
-        <v>30000</v>
-      </c>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
+        <v>626000</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>249000</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>249000</v>
+      </c>
       <c r="BF3" t="n">
-        <v>1475000</v>
+        <v>1346000</v>
       </c>
       <c r="BG3" t="n">
-        <v>2475000</v>
-      </c>
-      <c r="BH3" t="inlineStr"/>
+        <v>1737000</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>375000</v>
+      </c>
       <c r="BI3" t="n">
-        <v>2475000</v>
+        <v>1362000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>32734000</v>
+        <v>27387000</v>
       </c>
       <c r="BK3" t="n">
-        <v>32734000</v>
+        <v>27387000</v>
       </c>
       <c r="BL3" t="n">
-        <v>32492000</v>
+        <v>27145000</v>
       </c>
       <c r="BM3" t="n">
         <v>242000</v>
@@ -1869,192 +1877,190 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
-        <v>112387138</v>
+        <v>112782052</v>
       </c>
       <c r="C4" t="n">
-        <v>112387138</v>
+        <v>112782052</v>
       </c>
       <c r="D4" t="n">
-        <v>834000</v>
+        <v>2202000</v>
       </c>
       <c r="E4" t="n">
-        <v>24665000</v>
+        <v>26754000</v>
       </c>
       <c r="F4" t="n">
-        <v>24665000</v>
+        <v>26754000</v>
       </c>
       <c r="G4" t="n">
-        <v>14693000</v>
+        <v>18769000</v>
       </c>
       <c r="H4" t="n">
-        <v>24665000</v>
+        <v>26754000</v>
       </c>
       <c r="I4" t="n">
-        <v>834000</v>
+        <v>2202000</v>
       </c>
       <c r="J4" t="n">
-        <v>24665000</v>
+        <v>26754000</v>
       </c>
       <c r="K4" t="n">
-        <v>24665000</v>
+        <v>26754000</v>
       </c>
       <c r="L4" t="n">
-        <v>24665000</v>
+        <v>26754000</v>
       </c>
       <c r="M4" t="n">
-        <v>24665000</v>
+        <v>26754000</v>
       </c>
       <c r="N4" t="n">
-        <v>2706000</v>
+        <v>2301000</v>
       </c>
       <c r="O4" t="n">
-        <v>2702000</v>
+        <v>2293000</v>
       </c>
       <c r="P4" t="n">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="Q4" t="n">
-        <v>12990000</v>
+        <v>13938000</v>
       </c>
       <c r="R4" t="n">
-        <v>8969000</v>
+        <v>10515000</v>
       </c>
       <c r="S4" t="n">
-        <v>8969000</v>
+        <v>10515000</v>
       </c>
       <c r="T4" t="n">
-        <v>17275000</v>
+        <v>20550000</v>
       </c>
       <c r="U4" t="n">
-        <v>623000</v>
+        <v>2605000</v>
       </c>
       <c r="V4" t="n">
-        <v>284000</v>
+        <v>444000</v>
       </c>
       <c r="W4" t="n">
-        <v>284000</v>
+        <v>444000</v>
       </c>
       <c r="X4" t="n">
-        <v>34000</v>
+        <v>14000</v>
       </c>
       <c r="Y4" t="n">
-        <v>34000</v>
+        <v>14000</v>
       </c>
       <c r="Z4" t="n">
-        <v>47000</v>
+        <v>1823000</v>
       </c>
       <c r="AA4" t="n">
-        <v>47000</v>
+        <v>1823000</v>
       </c>
       <c r="AB4" t="n">
-        <v>258000</v>
+        <v>324000</v>
       </c>
       <c r="AC4" t="n">
-        <v>16652000</v>
+        <v>17945000</v>
       </c>
       <c r="AD4" t="n">
-        <v>1300000</v>
-      </c>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
+        <v>871000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>605000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>605000</v>
+      </c>
       <c r="AG4" t="n">
-        <v>787000</v>
+        <v>379000</v>
       </c>
       <c r="AH4" t="n">
-        <v>787000</v>
+        <v>379000</v>
       </c>
       <c r="AI4" t="n">
-        <v>5997000</v>
+        <v>6258000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>8568000</v>
+        <v>9832000</v>
       </c>
       <c r="AK4" t="n">
-        <v>8568000</v>
+        <v>9832000</v>
       </c>
       <c r="AL4" t="n">
-        <v>1815000</v>
+        <v>1323000</v>
       </c>
       <c r="AM4" t="n">
-        <v>6753000</v>
+        <v>8509000</v>
       </c>
       <c r="AN4" t="n">
-        <v>41940000</v>
+        <v>47304000</v>
       </c>
       <c r="AO4" t="n">
-        <v>10595000</v>
+        <v>10590000</v>
       </c>
       <c r="AP4" t="n">
-        <v>3338000</v>
+        <v>3974000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3338000</v>
+        <v>3974000</v>
       </c>
       <c r="AR4" t="n">
-        <v>5810000</v>
+        <v>3421000</v>
       </c>
       <c r="AS4" t="n">
-        <v>5809000</v>
+        <v>3419000</v>
       </c>
       <c r="AT4" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="AU4" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="AV4" t="n">
-        <v>1447000</v>
+        <v>3195000</v>
       </c>
       <c r="AW4" t="n">
-        <v>-2435000</v>
+        <v>-2934000</v>
       </c>
       <c r="AX4" t="n">
-        <v>3882000</v>
+        <v>6129000</v>
       </c>
       <c r="AY4" t="n">
         <v>2332000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1186000</v>
+        <v>3488000</v>
       </c>
       <c r="BA4" t="n">
-        <v>364000</v>
+        <v>309000</v>
       </c>
       <c r="BB4" t="n">
-        <v>31345000</v>
+        <v>36714000</v>
       </c>
       <c r="BC4" t="n">
-        <v>626000</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>249000</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>249000</v>
-      </c>
+        <v>30000</v>
+      </c>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
       <c r="BF4" t="n">
-        <v>1346000</v>
+        <v>1475000</v>
       </c>
       <c r="BG4" t="n">
-        <v>1737000</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>375000</v>
-      </c>
+        <v>2475000</v>
+      </c>
+      <c r="BH4" t="inlineStr"/>
       <c r="BI4" t="n">
-        <v>1362000</v>
+        <v>2475000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>27387000</v>
+        <v>32734000</v>
       </c>
       <c r="BK4" t="n">
-        <v>27387000</v>
+        <v>32734000</v>
       </c>
       <c r="BL4" t="n">
-        <v>27145000</v>
+        <v>32492000</v>
       </c>
       <c r="BM4" t="n">
         <v>242000</v>
@@ -2062,193 +2068,187 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
-        <v>112387138</v>
+        <v>112782052</v>
       </c>
       <c r="C5" t="n">
-        <v>112387138</v>
+        <v>112782052</v>
       </c>
       <c r="D5" t="n">
-        <v>1574000</v>
+        <v>2770000</v>
       </c>
       <c r="E5" t="n">
-        <v>24180000</v>
+        <v>30144000</v>
       </c>
       <c r="F5" t="n">
-        <v>24180000</v>
+        <v>30144000</v>
       </c>
       <c r="G5" t="n">
-        <v>20083000</v>
+        <v>23654000</v>
       </c>
       <c r="H5" t="n">
-        <v>24180000</v>
+        <v>30144000</v>
       </c>
       <c r="I5" t="n">
-        <v>1574000</v>
+        <v>2770000</v>
       </c>
       <c r="J5" t="n">
-        <v>24180000</v>
+        <v>30144000</v>
       </c>
       <c r="K5" t="n">
-        <v>24180000</v>
+        <v>30144000</v>
       </c>
       <c r="L5" t="n">
-        <v>24180000</v>
+        <v>30144000</v>
       </c>
       <c r="M5" t="n">
-        <v>24180000</v>
+        <v>30144000</v>
       </c>
       <c r="N5" t="n">
-        <v>1034000</v>
+        <v>3459000</v>
       </c>
       <c r="O5" t="n">
-        <v>1033000</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1000</v>
-      </c>
+        <v>3459000</v>
+      </c>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>12470000</v>
+        <v>16449000</v>
       </c>
       <c r="R5" t="n">
-        <v>10676000</v>
+        <v>10236000</v>
       </c>
       <c r="S5" t="n">
-        <v>10676000</v>
+        <v>10236000</v>
       </c>
       <c r="T5" t="n">
-        <v>15286000</v>
+        <v>21090000</v>
       </c>
       <c r="U5" t="n">
-        <v>1339000</v>
+        <v>3069000</v>
       </c>
       <c r="V5" t="n">
-        <v>218000</v>
+        <v>390000</v>
       </c>
       <c r="W5" t="n">
-        <v>218000</v>
+        <v>390000</v>
       </c>
       <c r="X5" t="n">
-        <v>35000</v>
+        <v>7000</v>
       </c>
       <c r="Y5" t="n">
-        <v>35000</v>
+        <v>7000</v>
       </c>
       <c r="Z5" t="n">
-        <v>834000</v>
+        <v>2180000</v>
       </c>
       <c r="AA5" t="n">
-        <v>834000</v>
+        <v>2180000</v>
       </c>
       <c r="AB5" t="n">
-        <v>252000</v>
+        <v>492000</v>
       </c>
       <c r="AC5" t="n">
-        <v>13947000</v>
+        <v>18021000</v>
       </c>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
-        <v>1364000</v>
+        <v>760000</v>
       </c>
       <c r="AF5" t="n">
-        <v>1364000</v>
+        <v>760000</v>
       </c>
       <c r="AG5" t="n">
-        <v>740000</v>
+        <v>590000</v>
       </c>
       <c r="AH5" t="n">
-        <v>740000</v>
+        <v>590000</v>
       </c>
       <c r="AI5" t="n">
-        <v>4593000</v>
+        <v>7429000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>7250000</v>
+        <v>9242000</v>
       </c>
       <c r="AK5" t="n">
-        <v>7250000</v>
+        <v>9242000</v>
       </c>
       <c r="AL5" t="n">
-        <v>1660000</v>
+        <v>1842000</v>
       </c>
       <c r="AM5" t="n">
-        <v>5590000</v>
+        <v>7400000</v>
       </c>
       <c r="AN5" t="n">
-        <v>39466000</v>
+        <v>50773000</v>
       </c>
       <c r="AO5" t="n">
-        <v>5436000</v>
+        <v>9098000</v>
       </c>
       <c r="AP5" t="n">
-        <v>2900000</v>
+        <v>4409000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2900000</v>
+        <v>4409000</v>
       </c>
       <c r="AR5" t="n">
-        <v>645000</v>
+        <v>816000</v>
       </c>
       <c r="AS5" t="n">
-        <v>643000</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>2000</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>2000</v>
-      </c>
+        <v>816000</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="n">
-        <v>1891000</v>
+        <v>3873000</v>
       </c>
       <c r="AW5" t="n">
-        <v>-1861000</v>
+        <v>-461000</v>
       </c>
       <c r="AX5" t="n">
-        <v>3752000</v>
+        <v>4334000</v>
       </c>
       <c r="AY5" t="n">
-        <v>2294000</v>
+        <v>662000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1149000</v>
+        <v>3678000</v>
       </c>
       <c r="BA5" t="n">
-        <v>309000</v>
+        <v>345000</v>
       </c>
       <c r="BB5" t="n">
-        <v>34030000</v>
+        <v>41675000</v>
       </c>
       <c r="BC5" t="n">
-        <v>626000</v>
+        <v>11000</v>
       </c>
       <c r="BD5" t="inlineStr"/>
       <c r="BE5" t="inlineStr"/>
       <c r="BF5" t="n">
-        <v>909000</v>
+        <v>1626000</v>
       </c>
       <c r="BG5" t="n">
-        <v>4682000</v>
+        <v>3647000</v>
       </c>
       <c r="BH5" t="n">
-        <v>3360000</v>
+        <v>187000</v>
       </c>
       <c r="BI5" t="n">
-        <v>1322000</v>
+        <v>3460000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>27813000</v>
+        <v>36391000</v>
       </c>
       <c r="BK5" t="n">
-        <v>27813000</v>
+        <v>36391000</v>
       </c>
       <c r="BL5" t="n">
-        <v>27616000</v>
+        <v>36365000</v>
       </c>
       <c r="BM5" t="n">
-        <v>197000</v>
+        <v>26000</v>
       </c>
     </row>
   </sheetData>
@@ -2434,398 +2434,398 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
-        <v>21269000</v>
+        <v>15411000</v>
       </c>
       <c r="C2" t="n">
-        <v>-2667000</v>
+        <v>-1635000</v>
       </c>
       <c r="D2" t="n">
-        <v>-1023000</v>
+        <v>-92000</v>
       </c>
       <c r="E2" t="n">
-        <v>5724000</v>
+        <v>3583000</v>
       </c>
       <c r="F2" t="n">
-        <v>26391000</v>
+        <v>27813000</v>
       </c>
       <c r="G2" t="n">
-        <v>27134000</v>
+        <v>21427000</v>
       </c>
       <c r="H2" t="n">
-        <v>-743000</v>
+        <v>6386000</v>
       </c>
       <c r="I2" t="n">
-        <v>-11862000</v>
+        <v>-8997000</v>
       </c>
       <c r="J2" t="n">
-        <v>-11862000</v>
+        <v>-8997000</v>
       </c>
       <c r="K2" t="n">
-        <v>-173000</v>
+        <v>-57000</v>
       </c>
       <c r="L2" t="n">
-        <v>-9022000</v>
+        <v>-7305000</v>
       </c>
       <c r="M2" t="n">
-        <v>-9022000</v>
+        <v>-7305000</v>
       </c>
       <c r="N2" t="n">
-        <v>-2667000</v>
+        <v>-1635000</v>
       </c>
       <c r="O2" t="n">
-        <v>-2667000</v>
+        <v>-1635000</v>
       </c>
       <c r="P2" t="n">
-        <v>-11173000</v>
+        <v>-120000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-11173000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>-4721000</v>
-      </c>
+        <v>-120000</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>-5000000</v>
+        <v>-28000</v>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="n">
-        <v>-5000000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>-429000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>-429000</v>
-      </c>
+        <v>-28000</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
       <c r="X2" t="n">
-        <v>-1023000</v>
+        <v>-92000</v>
       </c>
       <c r="Y2" t="n">
-        <v>-1023000</v>
+        <v>-92000</v>
       </c>
       <c r="Z2" t="n">
-        <v>22292000</v>
+        <v>15503000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-5724000</v>
+        <v>-3583000</v>
       </c>
       <c r="AB2" t="n">
-        <v>1129000</v>
+        <v>59000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-69603000</v>
+        <v>-38561000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-69603000</v>
+        <v>-38561000</v>
       </c>
       <c r="AE2" t="n">
-        <v>96490000</v>
-      </c>
-      <c r="AF2" t="inlineStr"/>
+        <v>57588000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>-290000</v>
+      </c>
       <c r="AG2" t="n">
-        <v>-1660000</v>
+        <v>-1321000</v>
       </c>
       <c r="AH2" t="n">
-        <v>98150000</v>
+        <v>59199000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
-        <v>16001000</v>
+        <v>15398000</v>
       </c>
       <c r="C3" t="n">
-        <v>-349000</v>
+        <v>-2692000</v>
       </c>
       <c r="D3" t="n">
-        <v>-203000</v>
+        <v>-764000</v>
       </c>
       <c r="E3" t="n">
-        <v>4612000</v>
+        <v>4934000</v>
       </c>
       <c r="F3" t="n">
-        <v>27134000</v>
+        <v>27387000</v>
       </c>
       <c r="G3" t="n">
-        <v>21787000</v>
+        <v>27813000</v>
       </c>
       <c r="H3" t="n">
-        <v>5347000</v>
+        <v>-426000</v>
       </c>
       <c r="I3" t="n">
-        <v>-6786000</v>
+        <v>-12464000</v>
       </c>
       <c r="J3" t="n">
-        <v>-6786000</v>
+        <v>-12464000</v>
       </c>
       <c r="K3" t="n">
-        <v>-810000</v>
+        <v>-781000</v>
       </c>
       <c r="L3" t="n">
-        <v>-5627000</v>
+        <v>-8991000</v>
       </c>
       <c r="M3" t="n">
-        <v>-5627000</v>
+        <v>-8991000</v>
       </c>
       <c r="N3" t="n">
-        <v>-349000</v>
+        <v>-2692000</v>
       </c>
       <c r="O3" t="n">
-        <v>-349000</v>
+        <v>-2692000</v>
       </c>
       <c r="P3" t="n">
-        <v>-4071000</v>
+        <v>-4124000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4071000</v>
+        <v>-4124000</v>
       </c>
       <c r="R3" t="n">
-        <v>-3194000</v>
+        <v>36000</v>
       </c>
       <c r="S3" t="n">
-        <v>-245000</v>
-      </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="n">
-        <v>-245000</v>
-      </c>
+        <v>504000</v>
+      </c>
+      <c r="T3" t="n">
+        <v>504000</v>
+      </c>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-429000</v>
+        <v>-3900000</v>
       </c>
       <c r="W3" t="n">
-        <v>-429000</v>
+        <v>-3900000</v>
       </c>
       <c r="X3" t="n">
-        <v>-203000</v>
+        <v>-764000</v>
       </c>
       <c r="Y3" t="n">
-        <v>-203000</v>
+        <v>-764000</v>
       </c>
       <c r="Z3" t="n">
-        <v>16204000</v>
+        <v>16162000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-4612000</v>
+        <v>-4934000</v>
       </c>
       <c r="AB3" t="n">
-        <v>728000</v>
+        <v>51000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-57973000</v>
+        <v>-50731000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-57973000</v>
+        <v>-50731000</v>
       </c>
       <c r="AE3" t="n">
-        <v>78061000</v>
+        <v>71776000</v>
       </c>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="n">
-        <v>-1607000</v>
+        <v>-1425000</v>
       </c>
       <c r="AH3" t="n">
-        <v>79668000</v>
+        <v>73201000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
-        <v>15398000</v>
+        <v>16001000</v>
       </c>
       <c r="C4" t="n">
-        <v>-2692000</v>
+        <v>-349000</v>
       </c>
       <c r="D4" t="n">
-        <v>-764000</v>
+        <v>-203000</v>
       </c>
       <c r="E4" t="n">
-        <v>4934000</v>
+        <v>4612000</v>
       </c>
       <c r="F4" t="n">
-        <v>27387000</v>
+        <v>27134000</v>
       </c>
       <c r="G4" t="n">
-        <v>27813000</v>
+        <v>21787000</v>
       </c>
       <c r="H4" t="n">
-        <v>-426000</v>
+        <v>5347000</v>
       </c>
       <c r="I4" t="n">
-        <v>-12464000</v>
+        <v>-6786000</v>
       </c>
       <c r="J4" t="n">
-        <v>-12464000</v>
+        <v>-6786000</v>
       </c>
       <c r="K4" t="n">
-        <v>-781000</v>
+        <v>-810000</v>
       </c>
       <c r="L4" t="n">
-        <v>-8991000</v>
+        <v>-5627000</v>
       </c>
       <c r="M4" t="n">
-        <v>-8991000</v>
+        <v>-5627000</v>
       </c>
       <c r="N4" t="n">
-        <v>-2692000</v>
+        <v>-349000</v>
       </c>
       <c r="O4" t="n">
-        <v>-2692000</v>
+        <v>-349000</v>
       </c>
       <c r="P4" t="n">
-        <v>-4124000</v>
+        <v>-4071000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4124000</v>
+        <v>-4071000</v>
       </c>
       <c r="R4" t="n">
-        <v>36000</v>
+        <v>-3194000</v>
       </c>
       <c r="S4" t="n">
-        <v>504000</v>
-      </c>
-      <c r="T4" t="n">
-        <v>504000</v>
-      </c>
-      <c r="U4" t="inlineStr"/>
+        <v>-245000</v>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="n">
+        <v>-245000</v>
+      </c>
       <c r="V4" t="n">
-        <v>-3900000</v>
+        <v>-429000</v>
       </c>
       <c r="W4" t="n">
-        <v>-3900000</v>
+        <v>-429000</v>
       </c>
       <c r="X4" t="n">
-        <v>-764000</v>
+        <v>-203000</v>
       </c>
       <c r="Y4" t="n">
-        <v>-764000</v>
+        <v>-203000</v>
       </c>
       <c r="Z4" t="n">
-        <v>16162000</v>
+        <v>16204000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-4934000</v>
+        <v>-4612000</v>
       </c>
       <c r="AB4" t="n">
-        <v>51000</v>
+        <v>728000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-50731000</v>
+        <v>-57973000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-50731000</v>
+        <v>-57973000</v>
       </c>
       <c r="AE4" t="n">
-        <v>71776000</v>
+        <v>78061000</v>
       </c>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="n">
-        <v>-1425000</v>
+        <v>-1607000</v>
       </c>
       <c r="AH4" t="n">
-        <v>73201000</v>
+        <v>79668000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
-        <v>15411000</v>
+        <v>21269000</v>
       </c>
       <c r="C5" t="n">
-        <v>-1635000</v>
+        <v>-2667000</v>
       </c>
       <c r="D5" t="n">
-        <v>-92000</v>
+        <v>-1023000</v>
       </c>
       <c r="E5" t="n">
-        <v>3583000</v>
+        <v>5724000</v>
       </c>
       <c r="F5" t="n">
-        <v>27813000</v>
+        <v>26391000</v>
       </c>
       <c r="G5" t="n">
-        <v>21427000</v>
+        <v>27134000</v>
       </c>
       <c r="H5" t="n">
-        <v>6386000</v>
+        <v>-743000</v>
       </c>
       <c r="I5" t="n">
-        <v>-8997000</v>
+        <v>-11862000</v>
       </c>
       <c r="J5" t="n">
-        <v>-8997000</v>
+        <v>-11862000</v>
       </c>
       <c r="K5" t="n">
-        <v>-57000</v>
+        <v>-173000</v>
       </c>
       <c r="L5" t="n">
-        <v>-7305000</v>
+        <v>-9022000</v>
       </c>
       <c r="M5" t="n">
-        <v>-7305000</v>
+        <v>-9022000</v>
       </c>
       <c r="N5" t="n">
-        <v>-1635000</v>
+        <v>-2667000</v>
       </c>
       <c r="O5" t="n">
-        <v>-1635000</v>
+        <v>-2667000</v>
       </c>
       <c r="P5" t="n">
-        <v>-120000</v>
+        <v>-11173000</v>
       </c>
       <c r="Q5" t="n">
-        <v>-120000</v>
-      </c>
-      <c r="R5" t="inlineStr"/>
+        <v>-11173000</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-4721000</v>
+      </c>
       <c r="S5" t="n">
-        <v>-28000</v>
+        <v>-5000000</v>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>-28000</v>
-      </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
+        <v>-5000000</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-429000</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-429000</v>
+      </c>
       <c r="X5" t="n">
-        <v>-92000</v>
+        <v>-1023000</v>
       </c>
       <c r="Y5" t="n">
-        <v>-92000</v>
+        <v>-1023000</v>
       </c>
       <c r="Z5" t="n">
-        <v>15503000</v>
+        <v>22292000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-3583000</v>
+        <v>-5724000</v>
       </c>
       <c r="AB5" t="n">
-        <v>59000</v>
+        <v>1129000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-38561000</v>
+        <v>-69603000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-38561000</v>
+        <v>-69603000</v>
       </c>
       <c r="AE5" t="n">
-        <v>57588000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>-290000</v>
-      </c>
+        <v>96490000</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="n">
-        <v>-1321000</v>
+        <v>-1660000</v>
       </c>
       <c r="AH5" t="n">
-        <v>59199000</v>
+        <v>98150000</v>
       </c>
     </row>
   </sheetData>
@@ -3385,207 +3385,207 @@
       </c>
       <c r="DE1" t="inlineStr">
         <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampStart</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>prevName</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>nameChangeDate</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="EN1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="EP1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="EQ1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="ER1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="ES1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampStart</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>prevName</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>nameChangeDate</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
         </is>
       </c>
       <c r="ET1" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. John Paul McMurdo M.B.A.', 'title': 'CEO, MD &amp; Director', 'fiscalYear': 2025, 'totalPay': 566505, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Mark  Simons C.A.', 'title': 'Chief Financial Officer', 'fiscalYear': 2025, 'totalPay': 374205, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Ludovic  Theau', 'title': 'Chief Investment Officer', 'fiscalYear': 2025, 'totalPay': 526485, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Maria  Loyez', 'title': 'Chief Customer Officer', 'fiscalYear': 2025, 'totalPay': 339613, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Anthony  Lane B.Com., L.L.M.', 'title': 'Chief Operating Officer', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Melanie  Hill', 'title': 'Head of Investor Relations', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Eveline  Moos B.Com.', 'title': 'Chief People &amp; Culture Officer', 'fiscalYear': 2025, 'totalPay': 254737, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. John  Woods C.F.A.', 'title': 'Deputy Chief Investment Officer &amp; Head of Multi Assets', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Clinton  Leong', 'title': 'Head of Investment Business Management', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Alison  George B.A., C.A.', 'title': 'Chief Impact &amp; Ethics Officer', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. John Paul McMurdo M.B.A.', 'title': 'CEO, MD &amp; Director', 'fiscalYear': 2025, 'totalPay': 561952, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Mark  Simons C.A.', 'title': 'Chief Financial Officer', 'fiscalYear': 2025, 'totalPay': 371198, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Ludovic  Theau', 'title': 'Chief Investment Officer', 'fiscalYear': 2025, 'totalPay': 522254, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Maria  Loyez', 'title': 'Chief Customer Officer', 'fiscalYear': 2025, 'totalPay': 336884, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Anthony  Lane B.Com., L.L.M.', 'title': 'Chief Operating Officer', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Melanie  Hill', 'title': 'Head of Investor Relations', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Eveline  Moos B.Com.', 'title': 'Chief People &amp; Culture Officer', 'fiscalYear': 2025, 'totalPay': 252689, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. John  Woods C.F.A.', 'title': 'Deputy Chief Investment Officer &amp; Head of Multi Assets', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Clinton  Leong', 'title': 'Head of Investment Business Management', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Alison  George B.A., C.A.', 'title': 'Chief Impact &amp; Ethics Officer', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="S2" t="n">
@@ -3698,34 +3698,34 @@
         <v>4</v>
       </c>
       <c r="W2" t="n">
-        <v>2.46</v>
+        <v>2.66</v>
       </c>
       <c r="X2" t="n">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.46</v>
+        <v>2.66</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="AE2" t="n">
         <v>0.1</v>
       </c>
       <c r="AF2" t="n">
-        <v>4.09</v>
+        <v>3.72</v>
       </c>
       <c r="AG2" t="n">
         <v>1772668800</v>
@@ -3737,10 +3737,10 @@
         <v>1.5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.326</v>
+        <v>1.333</v>
       </c>
       <c r="AK2" t="n">
-        <v>18.615385</v>
+        <v>19.692308</v>
       </c>
       <c r="AL2" t="n">
         <v>455</v>
@@ -3749,25 +3749,25 @@
         <v>455</v>
       </c>
       <c r="AN2" t="n">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="AO2" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="AS2" t="n">
-        <v>275468800</v>
+        <v>291404992</v>
       </c>
       <c r="AT2" t="n">
-        <v>284158585</v>
+        <v>305133062</v>
       </c>
       <c r="AU2" t="n">
         <v>2.34</v>
@@ -3782,19 +3782,19 @@
         <v>1.62</v>
       </c>
       <c r="AY2" t="n">
-        <v>2.1792555</v>
+        <v>2.3053281</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2.6212</v>
+        <v>2.5504</v>
       </c>
       <c r="BA2" t="n">
-        <v>3.1246</v>
+        <v>3.016</v>
       </c>
       <c r="BB2" t="n">
         <v>0.17</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.06910569</v>
+        <v>0.06390978</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>241938992</v>
+        <v>253322000</v>
       </c>
       <c r="BG2" t="n">
         <v>0.19014</v>
@@ -3820,16 +3820,16 @@
         <v>0.20818001</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.100039996</v>
+        <v>0.09955</v>
       </c>
       <c r="BL2" t="n">
         <v>113830079</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.2502505</v>
+        <v>0.24847569</v>
       </c>
       <c r="BN2" t="n">
-        <v>9.670311</v>
+        <v>10.302818</v>
       </c>
       <c r="BO2" t="n">
         <v>1751241600</v>
@@ -3850,16 +3850,16 @@
         <v>0.13</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.914</v>
+        <v>2.004</v>
       </c>
       <c r="BV2" t="n">
-        <v>5.644</v>
+        <v>5.91</v>
       </c>
       <c r="BW2" t="n">
-        <v>-0.30459768</v>
+        <v>-0.20833331</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.27449715</v>
+        <v>0.24487448</v>
       </c>
       <c r="BY2" t="n">
         <v>0.08</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="CB2" t="n">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
@@ -3975,156 +3975,156 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="DE2" t="n">
+        <v>-3.759404</v>
       </c>
       <c r="DF2" t="n">
-        <v>1780467042</v>
-      </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
+        <v>2.56</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>-0.10000014</v>
       </c>
       <c r="DH2" t="inlineStr">
         <is>
+          <t>2.56 - 2.56</t>
+        </is>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>Frankfurt</t>
+        </is>
+      </c>
+      <c r="DJ2" t="n">
+        <v>64</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>0.22000003</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>0.09401711</v>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>2.34 - 4.52</t>
+        </is>
+      </c>
+      <c r="DN2" t="n">
+        <v>-1.96</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>-0.43362832</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>-20.833332</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>1772139600</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>1772139600</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>1772064000</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>1772064000</v>
+      </c>
+      <c r="DU2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>0.009599923999999999</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>0.0037640857</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>-0.4560001</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>-0.15119366</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>Australian Ethical Investment Ltd.</t>
+        </is>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
           <t>Australian Ethical Inv.       R</t>
         </is>
       </c>
-      <c r="DI2" t="inlineStr">
+      <c r="EF2" t="inlineStr">
         <is>
           <t>Australian Ethical Investment Limited</t>
         </is>
-      </c>
-      <c r="DJ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>FRA</t>
-        </is>
-      </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>finmb_9248443</t>
-        </is>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>Europe/Berlin</t>
-        </is>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>CEST</t>
-        </is>
-      </c>
-      <c r="DO2" t="n">
-        <v>7200000</v>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>dr_market</t>
-        </is>
-      </c>
-      <c r="DQ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>1613458800000</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>-0.03999996</v>
-      </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>2.42 - 2.42</t>
-        </is>
-      </c>
-      <c r="DU2" t="inlineStr">
-        <is>
-          <t>Frankfurt</t>
-        </is>
-      </c>
-      <c r="DV2" t="n">
-        <v>93</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>0.08000016</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>0.034188103</v>
-      </c>
-      <c r="DY2" t="inlineStr">
-        <is>
-          <t>2.34 - 4.52</t>
-        </is>
-      </c>
-      <c r="DZ2" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>-0.46460176</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>-30.459768</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>1772139600</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>1772139600</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>1772064000</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>1772064000</v>
       </c>
       <c r="EG2" t="b">
         <v>0</v>
       </c>
-      <c r="EH2" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>-0.20120001</v>
+      <c r="EH2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="EI2" t="b">
+        <v>0</v>
       </c>
       <c r="EJ2" t="n">
-        <v>-0.07675873499999999</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>-0.70459986</v>
+        <v>1613458800000</v>
+      </c>
+      <c r="EK2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="EL2" t="n">
-        <v>-0.22550082</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>15</v>
+        <v>1782108335</v>
+      </c>
+      <c r="EM2" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="EN2" t="inlineStr">
+        <is>
+          <t>finmb_9248443</t>
+        </is>
       </c>
       <c r="EO2" t="inlineStr">
         <is>
-          <t>Australian Ethical Investment Ltd.</t>
+          <t>Europe/Berlin</t>
         </is>
       </c>
       <c r="EP2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="EQ2" t="b">
+          <t>CEST</t>
+        </is>
+      </c>
+      <c r="EQ2" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="ER2" t="inlineStr">
+        <is>
+          <t>dr_market</t>
+        </is>
+      </c>
+      <c r="ES2" t="b">
         <v>0</v>
-      </c>
-      <c r="ER2" t="n">
-        <v>-1.6260147</v>
-      </c>
-      <c r="ES2" t="n">
-        <v>2.42</v>
       </c>
       <c r="ET2" t="inlineStr"/>
     </row>
